--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_15_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_15_6.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9995347025149675</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3619850961467276</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9969908847168731</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999777885611426</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9993313347962697</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002762206869201112</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3787532077360805</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001088171293281695</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J2" t="n">
-        <v>2.309298874365622e-05</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005556364995477225</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003928337648342752</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01661988829445346</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000859010741598</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01732743134706</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P2" t="n">
-        <v>90.38862084291776</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q2" t="n">
-        <v>135.4870263630412</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_1</t>
+          <t>model_15_6_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9995346860577581</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3619847015914484</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9969900470103028</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999777565872311</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9993311377590863</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002762304566304812</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3787534419611381</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001088474228914344</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J3" t="n">
-        <v>2.312623166783855e-05</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005558002302910912</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003930274017603147</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01662018220810112</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000859041124139</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01732773777322013</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P3" t="n">
-        <v>90.3885501057278</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q3" t="n">
-        <v>135.4869556258512</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_2</t>
+          <t>model_15_6_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9997849330725581</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C4" t="n">
-        <v>0.346878371432804</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D4" t="n">
-        <v>0.998507435987482</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E4" t="n">
-        <v>0.999756279407979</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9995227629681573</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001276730185370144</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H4" t="n">
-        <v>0.387721212102794</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005397484506208808</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002533936195791607</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003965666410459174</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004998286269435355</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01129924858284897</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000397046635277</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01178028098768992</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P4" t="n">
-        <v>91.93207621027153</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q4" t="n">
-        <v>137.030481730395</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_3</t>
+          <t>model_15_6_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9997842372440839</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3466091591338206</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9985085199337653</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9997525383950586</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9995206531912108</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000128086092377537</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3878810281528363</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005393564685537708</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002572831095763648</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003983197890650678</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005003292578245309</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01131751264092676</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000398331241691</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0117993225845319</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P5" t="n">
-        <v>91.92561584687387</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q5" t="n">
-        <v>137.0240213669973</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_4</t>
+          <t>model_15_6_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9997835633370022</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3463626482236063</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9985091764768663</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9997491926425982</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9995187029738185</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001284861527324743</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3880273676778564</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000539119046159452</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002607616516196449</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003999403488895484</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005007646200281104</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01133517325551199</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000399575377842</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01181773504804254</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P6" t="n">
-        <v>91.91937884054478</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q6" t="n">
-        <v>137.0177843606682</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_5</t>
+          <t>model_15_6_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9997829214793715</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3461374190243431</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9985096279436046</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9997461692177518</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9995169071548075</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001288671871488914</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3881610734599338</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000538955784503355</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002639050731868463</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004014326092667686</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005011545837021313</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01135196842617576</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000400760345776</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01183524522389226</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P7" t="n">
-        <v>91.91345648189157</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q7" t="n">
-        <v>137.011862002015</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_6</t>
+          <t>model_15_6_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9997823065634569</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3459317748379119</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D8" t="n">
-        <v>0.998509765869105</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9997434588743896</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9995152462322973</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000129232227798758</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3882831527323657</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005389059071952251</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002667229873776475</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000402812775550884</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005014753728754156</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01136803535351461</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000401895575157</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01185199615359105</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P8" t="n">
-        <v>91.90779911310838</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q8" t="n">
-        <v>137.0062046332318</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_7</t>
+          <t>model_15_6_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9997817264228409</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3457438794752201</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9985096807412198</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9997410388926466</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9995137117751928</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001295766243291988</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3883946955363166</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005389366915661266</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002692390157858344</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0004040878536759805</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005017604756084027</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01138317285861894</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000402966603986</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01186777809362662</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P9" t="n">
-        <v>91.90247631628918</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q9" t="n">
-        <v>137.0008818364126</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_8</t>
+          <t>model_15_6_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9997811918709341</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3455732621444344</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D10" t="n">
-        <v>0.998509535429691</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9997388748902443</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F10" t="n">
-        <v>0.999512325173013</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001298939574325316</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3884959813541559</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005389892398467366</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0002714889052882197</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0004052400697283213</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005019970981553441</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01139710302807391</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000403953469045</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01188230129923472</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P10" t="n">
-        <v>91.89758430488051</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q10" t="n">
-        <v>136.9959898250039</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_9</t>
+          <t>model_15_6_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.999780681027817</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3454177515910798</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9985091984651883</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997369206272099</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9995110304796953</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001301972159741311</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3885882991363333</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0005391110946326767</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002735207310761389</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0004063159128544078</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005022192275817345</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0114103994660192</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00040489656403</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01189616379407076</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P11" t="n">
-        <v>91.89292042221116</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q11" t="n">
-        <v>136.9913259423346</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_10</t>
+          <t>model_15_6_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9997802097195051</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3452770418453652</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D12" t="n">
-        <v>0.998508823464999</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9997351686077395</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9995098528320664</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000130477004947549</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H12" t="n">
-        <v>0.388671830519734</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000539246704073509</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002753422864542469</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000407294495263878</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005024116178937426</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0114226531483517</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000405766671683</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01190893914102878</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P12" t="n">
-        <v>91.88862710805266</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q12" t="n">
-        <v>136.9870326281761</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_11</t>
+          <t>model_15_6_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9997797801048744</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3451489740818764</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D13" t="n">
-        <v>0.998508450480208</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9997336018832714</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9995087909501186</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001307320427506757</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3887478570763803</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0005393815846959423</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002769711926560585</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0004081768805968602</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005025674715395576</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0114338113833785</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000406559806386</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0119205724052214</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P13" t="n">
-        <v>91.88472160958058</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q13" t="n">
-        <v>136.983127129704</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9997793830128308</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C14" t="n">
-        <v>0.345033007978323</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9985080863119186</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9997321792084407</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9995078196886641</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001309677737412743</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3888166995649244</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0005395132770510762</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002784503320338551</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0004089839635910081</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005027183606552421</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01144411524501891</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000407292899389</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01193131492358377</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P14" t="n">
-        <v>91.88111853400315</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q14" t="n">
-        <v>136.9795240541266</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_13</t>
+          <t>model_15_6_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999779014946073</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3449277503183523</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9985076748606898</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9997309018504446</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9995069298805093</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001311862740683351</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3888791850587772</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0005396620680988153</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0002797783870966474</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0004097233618513465</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005028529291468404</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01145365767204237</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N15" t="n">
-        <v>1.00040797240725</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01194126359148117</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P15" t="n">
-        <v>91.87778461061752</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q15" t="n">
-        <v>136.9761901307409</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_14</t>
+          <t>model_15_6_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9997786827127484</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C16" t="n">
-        <v>0.344832428840277</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9985072677472947</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9997297714224921</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9995061404739832</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001313835021215558</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3889357720058362</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0005398092904774885</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002809536806087053</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0004103793300046355</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005029619767175649</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01146226426678236</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N16" t="n">
-        <v>1.00040858576108</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01195023658677735</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P16" t="n">
-        <v>91.87478002885376</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q16" t="n">
-        <v>136.9731855489772</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_15</t>
+          <t>model_15_6_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9997783805300907</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3447465660283279</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9985069074093759</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9997287481156224</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9995054192997606</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001315628908007914</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3889867438800895</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0005399395976748662</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0002820176015088817</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000410978599591874</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005030496947879774</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01147008678261814</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000409143636756</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0119583921233071</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P17" t="n">
-        <v>91.87205112726933</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q17" t="n">
-        <v>136.9704566473928</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_16</t>
+          <t>model_15_6_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9997781025035462</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3446689965882368</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9985065398400788</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9997278266197231</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9995047628382195</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001317279393677413</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3890327924505529</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0005400725199193677</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0002829756706625461</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0004115240952909569</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005031373328433664</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01147727926678363</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N18" t="n">
-        <v>1.00040965691653</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O18" t="n">
-        <v>0.011965890806414</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P18" t="n">
-        <v>91.86954365538413</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q18" t="n">
-        <v>136.9679491755076</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_17</t>
+          <t>model_15_6_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9997778508861549</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3445987889027629</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9985062089913047</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9997269982149808</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9995041726039476</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001318773103204731</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3890744707654643</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0005401921631049849</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0002838369539641484</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0004120145585345667</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L19" t="n">
-        <v>0.005032082017992467</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0114837846688482</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000410121440945</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01197267315691251</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P19" t="n">
-        <v>91.86727706973919</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q19" t="n">
-        <v>136.9656825898626</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_18</t>
+          <t>model_15_6_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.999777622308509</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C20" t="n">
-        <v>0.344535312665294</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9985058922918341</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9997262555568326</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9995036390908871</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0001320130038851758</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3891121530020565</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000540306689548822</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0002846090874745113</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0004124578885116666</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L20" t="n">
-        <v>0.005032726879824055</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01148969120060134</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000410543430445</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01197883114195058</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P20" t="n">
-        <v>91.86522025189697</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q20" t="n">
-        <v>136.9636257720204</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_19</t>
+          <t>model_15_6_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9997774125239768</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3444779720029595</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D21" t="n">
-        <v>0.998505584052458</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9997255835200844</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9995031515988959</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001321375410457189</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3891461928962059</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0005404181566110491</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0002853077966918517</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0004128629766514504</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0050333520391044</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01149510944035414</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000410930724966</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01198448004738696</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P21" t="n">
-        <v>91.86333440048139</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q21" t="n">
-        <v>136.9617399206048</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_20</t>
+          <t>model_15_6_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9997772230768702</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3444262114629796</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9985052782858362</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9997249895398913</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9995027134765424</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G22" t="n">
-        <v>0.000132250005031825</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3891769201886769</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0005405287294635031</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002859253513672715</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0004132270404153874</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L22" t="n">
-        <v>0.005033756056643097</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M22" t="n">
-        <v>0.011500000218775</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N22" t="n">
-        <v>1.00041128047347</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0119895790363705</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P22" t="n">
-        <v>91.86163289835608</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q22" t="n">
-        <v>136.9600384184795</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_21</t>
+          <t>model_15_6_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9997770534689556</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3443796221518178</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9985050509076369</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9997244434000956</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9995023223396045</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001323506916166334</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H23" t="n">
-        <v>0.389204577616336</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0005406109551032784</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002864931669075493</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0004135520610054139</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005034256793072214</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01150437706338911</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000411593595774</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01199414221232115</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P23" t="n">
-        <v>91.86011080728159</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q23" t="n">
-        <v>136.958516327405</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_22</t>
+          <t>model_15_6_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9997768988410475</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3443375278085861</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9985048360500763</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9997239502546668</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9995019670799484</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0001324424854224762</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3892295666368593</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0005406886529671239</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0002870058847872884</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0004138472688772062</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00503464671323263</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01150836588845159</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000411879062681</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01199830084992455</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P24" t="n">
-        <v>91.85872415811568</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q24" t="n">
-        <v>136.9571296782391</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_15_6_23</t>
+          <t>model_15_6_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9997767619986414</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3442993348550757</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9985046520931646</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9997235130724902</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9995016535542612</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001325237209859716</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3892522396239128</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0005407551763840127</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000287460418289062</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0004141077973365373</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L25" t="n">
-        <v>0.005035044284648321</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01151189476089716</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000412131694816</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0120019799537759</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P25" t="n">
-        <v>91.85749780450415</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q25" t="n">
-        <v>136.9559033246276</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9997766301774558</v>
+        <v>0.9994833690424757</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3442646831620988</v>
+        <v>0.6097840175530888</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9985044176200105</v>
+        <v>0.999498245261547</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9997231137296294</v>
+        <v>0.9999842378001504</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9995013527085415</v>
+        <v>0.9997087371111711</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000132601975736168</v>
+        <v>0.0003066944536817387</v>
       </c>
       <c r="H26" t="n">
-        <v>0.389272810365739</v>
+        <v>0.2316490636332266</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0005408399677367481</v>
+        <v>0.0005929986157139594</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0002878756106702543</v>
+        <v>9.18619780272122e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0004143577892035012</v>
+        <v>0.0003010924067769765</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005035399951895722</v>
+        <v>0.003926839555606831</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01151529312419654</v>
+        <v>0.01751269407263596</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000412375057005</v>
+        <v>1.000953780229276</v>
       </c>
       <c r="O26" t="n">
-        <v>0.01200552299243651</v>
+        <v>0.01825824571558247</v>
       </c>
       <c r="P26" t="n">
-        <v>91.85631716070483</v>
+        <v>90.17931714172472</v>
       </c>
       <c r="Q26" t="n">
-        <v>136.9547226808282</v>
+        <v>135.2777226618481</v>
       </c>
     </row>
   </sheetData>
